--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками работы и (или) сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики работы и (или) сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с измененными графиками работы и (или) сменности</t>
+          <t>Лист ознакомления с измененными графиками работы / сменности</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении норм времени на технологические операции</t>
+          <t>ЛНА об установлении норм времени на технологические операции</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении норм времени на технологические операции</t>
+          <t>ЛНА об установлении норм времени на технологические операции</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Наряд (вызов) на работу (смену, поездку)</t>
+          <t>Наряд / вызов / сообщение о явке на работу</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Сообщение (вызов) о явке на работу</t>
+          <t>Наряд / вызов / сообщение о явке на работу</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на предоставление еженедельных дней отдыха в суммированном виде</t>
+          <t>Письменное согласие на предоставление / перенос суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета служебного времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об установлении продолжительности смены</t>
+          <t>Приказ (ЛНА) об установлении продолжительности смены / рабочего времени</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Документы учета служебного времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об установлении продолжительности смены</t>
+          <t>Приказ (ЛНА) об установлении продолжительности смены / рабочего времени</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета</t>
+          <t>Приказ (ЛНА) об увеличении учетного периода суммированного учета</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета</t>
+          <t>Приказ (ЛНА) об увеличении учетного периода суммированного учета</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) до 12 часов</t>
+          <t>ЛНА об увеличении продолжительности ежедневной работы (смены) / работы на судне</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) до 12 часов</t>
+          <t>ЛНА об увеличении продолжительности ежедневной работы (смены) / работы на судне</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении рабочего дня (смены) на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении рабочего дня (смены) на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на разделение рабочего дня (смены) на части</t>
+          <t>Письменное согласие на разделение рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении ненормированного рабочего дня</t>
+          <t>ЛНА об установлении ненормированного рабочего дня</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности подготовительно-заключительного времени и медицинских осмотров</t>
+          <t>ЛНА о подготовительно-заключительном времени / медицинских осмотрах / иных видах времени</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности подготовительно-заключительного времени и медицинских осмотров</t>
+          <t>ЛНА о подготовительно-заключительном времени / медицинских осмотрах / иных видах времени</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об иных видах времени, включаемых в рабочее время</t>
+          <t>ЛНА о подготовительно-заключительном времени / медицинских осмотрах / иных видах времени</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об иных видах времени, включаемых в рабочее время</t>
+          <t>ЛНА о подготовительно-заключительном времени / медицинских осмотрах / иных видах времени</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о размере дополнительного вознаграждения за время в составе экипажа без управления</t>
+          <t>ЛНА о дополнительном вознаграждении за время в составе экипажа без управления</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о размере дополнительного вознаграждения за время в составе экипажа без управления</t>
+          <t>ЛНА о дополнительном вознаграждении за время в составе экипажа без управления</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о перечне простейших неисправностей, устраняемых на линии</t>
+          <t>ЛНА о перечне простейших неисправностей на линии</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности подготовительно-заключительного времени и медицинских осмотров</t>
+          <t>ЛНА о подготовительно-заключительном времени / медицинских осмотрах / иных видах времени</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности подготовительно-заключительного времени и медицинских осмотров</t>
+          <t>ЛНА о подготовительно-заключительном времени / медицинских осмотрах / иных видах времени</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета</t>
+          <t>Приказ (ЛНА) об увеличении учетного периода суммированного учета</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета</t>
+          <t>Приказ (ЛНА) об увеличении учетного периода суммированного учета</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) до 12 часов</t>
+          <t>ЛНА об увеличении продолжительности ежедневной работы (смены) / работы на судне</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) до 12 часов</t>
+          <t>ЛНА об увеличении продолжительности ежедневной работы (смены) / работы на судне</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении рабочего дня (смены) на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении рабочего дня (смены) на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на разделение рабочего дня (смены) на части</t>
+          <t>Письменное согласие на разделение рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Согласование сокращения ежедневного (междусменного) отдыха</t>
+          <t>Письменное согласие / согласование на сокращение междусменного отдыха</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Руководство по производству полетов (РПП) в части режима рабочего времени и времени отдыха</t>
+          <t>РПП (режим рабочего времени и времени отдыха)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Руководство по производству полетов (РПП) в части режима рабочего времени и времени отдыха</t>
+          <t>РПП (режим рабочего времени и времени отдыха)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Расписания движения гражданских воздушных судов</t>
+          <t>Расписание занятий / выполнения работ / движения ВС</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Графики работы</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Графики работы</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками работы</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики работы</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики работы</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с измененными графиками работы</t>
+          <t>Лист ознакомления с измененными графиками работы / сменности</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета</t>
+          <t>Приказ (ЛНА) об увеличении учетного периода суммированного учета</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета</t>
+          <t>Приказ (ЛНА) об увеличении учетного периода суммированного учета</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к сверхурочной работе</t>
+          <t>Письменное согласие на привлечение к сверхурочной работе / работе в выходные / вне графика</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Согласование привлечения к сверхурочной работе</t>
+          <t>Согласование привлечения к сверхурочной работе / работе в выходной день</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на увеличение продолжительности полетного времени</t>
+          <t>Письменное согласие на увеличение продолжительности работы / поездки / полетного времени</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Согласование увеличения продолжительности полетного времени</t>
+          <t>Письменное согласие на увеличение продолжительности работы / поездки / полетного времени</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении полетной смены на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении полетной смены на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на разделение полетной смены на части</t>
+          <t>Письменное согласие на разделение рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Документы (система) учета рабочего и полетного времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Табель учета рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к работе в выходные и нерабочие праздничные дни</t>
+          <t>Письменное согласие на привлечение к сверхурочной работе / работе в выходные / вне графика</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Письменное распоряжение (приказ) о привлечении к работе в выходные и нерабочие праздничные дни</t>
+          <t>Приказ / распоряжение о привлечении к сверхурочной работе / работе в выходные</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Согласование привлечения к работе в выходной день</t>
+          <t>Согласование привлечения к сверхурочной работе / работе в выходной день</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками работы и (или) сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Документы учета рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>График работы (дежурств на дому)</t>
+          <t>Графики дежурств / несения дежурства</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>График работы (дежурств на дому)</t>
+          <t>Графики дежурств / несения дежурства</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о порядке учета времени следования при дежурстве на дому</t>
+          <t>ЛНА о нормативном времени прибытия / учете времени следования при дежурстве на дому</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о порядке учета времени следования при дежурстве на дому</t>
+          <t>ЛНА о нормативном времени прибытия / учете времени следования при дежурстве на дому</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Документы учета времени дежурства на дому</t>
+          <t>Документы / журнал учета времени дежурства на дому</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Документы учета времени дежурства на дому</t>
+          <t>Документы / журнал учета времени дежурства на дому</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Графики работы на вахте</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об увеличении продолжительности работы на судне до 180 календарных дней</t>
+          <t>ЛНА об увеличении продолжительности ежедневной работы (смены) / работы на судне</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об увеличении продолжительности работы на судне до 180 календарных дней</t>
+          <t>ЛНА об увеличении продолжительности ежедневной работы (смены) / работы на судне</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение (приказ) об установлении суточного дежурства</t>
+          <t>Распоряжение (приказ) об установлении суточного / круглосуточного дежурства</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на выполнение работ, не входящих в круг должностных обязанностей</t>
+          <t>Письменное согласие на работы вне должностных обязанностей / саморемонт</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Заявление о предоставлении дней отдыха в период работы на судне</t>
+          <t>Заявление о предоставлении / замене дней отдыха</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Заявление о предоставлении дней отдыха в период работы на судне</t>
+          <t>Заявление о предоставлении / замене дней отдыха</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Порядок предоставления выходных, праздничных и суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Порядок предоставления выходных, праздничных и суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Учетные записи рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Учетные записи рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Учетные записи рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение о производстве аварийных и авральных работ</t>
+          <t>Распоряжение о производстве аварийных / авральных работ</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Табель учета рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение о приостановлении действия графика работы на вахте</t>
+          <t>Распоряжение о производстве аварийных / авральных работ</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Порядок введения суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Порядок введения суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Графики работы на вахте</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Графики работы на вахте</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Расписания выполнения работ</t>
+          <t>Расписание занятий / выполнения работ / движения ВС</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Расписания выполнения работ</t>
+          <t>Расписание занятий / выполнения работ / движения ВС</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении работы со сменой экипажа</t>
+          <t>ЛНА об установлении работы со сменой экипажа</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности периода нахождения на борту между вахтами</t>
+          <t>ЛНА о периоде нахождения на борту / двухсменном режиме</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности периода нахождения на борту между вахтами</t>
+          <t>ЛНА о периоде нахождения на борту / двухсменном режиме</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на выполнение работ, не входящих в круг должностных обязанностей</t>
+          <t>Письменное согласие на работы вне должностных обязанностей / саморемонт</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности периода работы в двухсменном режиме</t>
+          <t>ЛНА о периоде нахождения на борту / двухсменном режиме</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности периода работы в двухсменном режиме</t>
+          <t>ЛНА о периоде нахождения на борту / двухсменном режиме</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на выполнение работ, не входящих в круг должностных обязанностей</t>
+          <t>Письменное согласие на работы вне должностных обязанностей / саморемонт</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Решение о переносе суммированных дней отдыха за пределы учетного периода</t>
+          <t>Решение / согласие о переносе суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Решение о переносе суммированных дней отдыха за пределы учетного периода</t>
+          <t>Решение / согласие о переносе суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на перенос суммированных дней отдыха</t>
+          <t>Письменное согласие на предоставление / перенос суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Заявление о предоставлении суммированных дней отдыха в период навигации</t>
+          <t>Заявление о предоставлении / замене дней отдыха</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Согласование предоставления суммированных дней отдыха</t>
+          <t>Письменное согласие на предоставление / перенос суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Графики предоставления суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Графики предоставления суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Графики предоставления суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Заявление о замене суммированных дней отдыха денежной компенсацией</t>
+          <t>Заявление о предоставлении / замене дней отдыха</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение о привлечении к аварийным (авральным) работам / о приостановлении графика работы на вахте</t>
+          <t>Распоряжение о производстве аварийных / авральных работ</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об отнесении иных работ к числу авральных</t>
+          <t>Перечень / ЛНА об авральных работах</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об отнесении иных работ к числу авральных</t>
+          <t>Перечень / ЛНА об авральных работах</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Табель учета рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Иные локальные нормативные акты о режиме рабочего времени и времени отдыха</t>
+          <t>Иные ЛНА о режиме рабочего времени и времени отдыха</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Графики работы</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>График работы руководителей организации</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Расписание занятий</t>
+          <t>Расписание занятий / выполнения работ / движения ВС</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Соглашение о продолжительности перерывов для отдыха и питания</t>
+          <t>Соглашение о продолжительности перерывов / видов времени отдыха</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Соглашение о продолжительности перерывов для отдыха и питания</t>
+          <t>Соглашение о продолжительности перерывов / видов времени отдыха</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Планы и графики организации (коллегиальные органы)</t>
+          <t>Планы / графики организации (коллегиальные органы)</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о порядке выполнения дополнительных видов работ за дополнительную оплату</t>
+          <t>ЛНА о дополнительных видах работ за дополнительную оплату</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Графики работы в каникулярное время</t>
+          <t>Графики работы / сменности (каникулярное время)</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на выполнение дополнительной работы за дополнительную оплату</t>
+          <t>Письменное согласие на выполнение дополнительной работы</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Графики работы в каникулярное время</t>
+          <t>Графики работы / сменности (каникулярное время)</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>График работы руководителей организации</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Соглашение о продолжительности перерывов для отдыха и питания</t>
+          <t>Соглашение о продолжительности перерывов / видов времени отдыха</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Соглашение о продолжительности перерывов для отдыха и питания</t>
+          <t>Соглашение о продолжительности перерывов / видов времени отдыха</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Графики работы</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Расписание занятий</t>
+          <t>Расписание занятий / выполнения работ / движения ВС</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности занятий и перерывов</t>
+          <t>ЛНА о продолжительности занятий и перерывов</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Планы и графики организации (коллегиальные органы)</t>
+          <t>Планы / графики организации (коллегиальные органы)</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о периодических кратковременных дежурствах</t>
+          <t>ЛНА о периодических кратковременных дежурствах</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Графики дежурств</t>
+          <t>Графики дежурств / несения дежурства</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на выполнение дополнительной работы за дополнительную оплату</t>
+          <t>Письменное согласие на выполнение дополнительной работы</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о режиме рабочего дня с разделением на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о режиме рабочего дня с разделением на части</t>
+          <t>ЛНА о разделении рабочего дня / смены / полетной смены на части</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Локальные нормативные акты и графики работ в каникулярное время</t>
+          <t>ЛНА / графики работ в каникулярное время</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Графики работы в каникулярное время</t>
+          <t>Графики работы / сменности (каникулярное время)</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на введение суммированного учета рабочего времени в каникулярное время</t>
+          <t>Письменное согласие на введение суммированного учета / работу в каникулярное время</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к работе в каникулярное время</t>
+          <t>Письменное согласие на введение суммированного учета / работу в каникулярное время</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о режиме 36-часовой рабочей недели</t>
+          <t>ЛНА о режиме 36-часовой рабочей недели</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Решение о круглосуточном режиме работы и (или) разделении года на производственные периоды</t>
+          <t>Решение о круглосуточном режиме / производственных периодах</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Соглашение о продолжительности видов времени отдыха</t>
+          <t>Соглашение о продолжительности перерывов / видов времени отдыха</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Соглашение о продолжительности видов времени отдыха</t>
+          <t>Соглашение о продолжительности перерывов / видов времени отдыха</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками работы и (или) сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Решение о предоставлении перерыва для сна</t>
+          <t>Решение о предоставлении перерыва для сна / уменьшении междусменного отдыха</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Решение о предоставлении перерыва для сна</t>
+          <t>Решение о предоставлении перерыва для сна / уменьшении междусменного отдыха</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Задание (распоряжение) о перемещении работника в качестве пассажира</t>
+          <t>Задание (распоряжение) о перемещении в качестве пассажира</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Графики работы и (или) сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками работы и (или) сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о времени приема и сдачи смены</t>
+          <t>ЛНА о времени приема и сдачи смены</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Приказ (распоряжение) о введении круглосуточного дежурства и (или) о вызове с междусменного отдыха</t>
+          <t>Распоряжение (приказ) об установлении суточного / круглосуточного дежурства</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Решение о предоставлении перерыва для сна</t>
+          <t>Решение о предоставлении перерыва для сна / уменьшении междусменного отдыха</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Решение о предоставлении перерыва для сна</t>
+          <t>Решение о предоставлении перерыва для сна / уменьшении междусменного отдыха</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Задание (распоряжение) о перемещении работника в качестве пассажира</t>
+          <t>Задание (распоряжение) о перемещении в качестве пассажира</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об обязательности использования СИЗ и времени переодевания</t>
+          <t>ЛНА о включении в рабочее время времени следования / душа / переодевания в СИЗ</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о включении в рабочее время времени для принятия душа</t>
+          <t>ЛНА о включении в рабочее время времени следования / душа / переодевания в СИЗ</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о включении в рабочее время времени следования по территории работодателя</t>
+          <t>ЛНА о включении в рабочее время времени следования / душа / переодевания в СИЗ</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении иной продолжительности смены</t>
+          <t>Приказ (ЛНА) об установлении продолжительности смены / рабочего времени</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении продолжительности смены до 24 часов</t>
+          <t>Приказ (ЛНА) об установлении продолжительности смены / рабочего времени</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Соглашение об определении места начала и окончания ежедневной работы (смены)</t>
+          <t>Соглашение об определении места начала / окончания смены</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Соглашение об определении места начала и окончания ежедневной работы (смены)</t>
+          <t>Соглашение об определении места начала / окончания смены</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении продолжительности рабочего времени при сменной работе</t>
+          <t>Приказ (ЛНА) об установлении продолжительности смены / рабочего времени</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении продолжительности рабочего времени при сменной работе</t>
+          <t>Приказ (ЛНА) об установлении продолжительности смены / рабочего времени</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на оплату переработки вместо дополнительного отдыха</t>
+          <t>Письменное согласие на оплату вместо дней отдыха / переработки</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт с перечнем железнодорожных линий (участков) для ночных работ</t>
+          <t>ЛНА с перечнем участков для ночных работ</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт с перечнем железнодорожных линий (участков) для ночных работ</t>
+          <t>ЛНА с перечнем участков для ночных работ</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к работе независимо от междусменного отдыха</t>
+          <t>Письменное согласие на привлечение к сверхурочной работе / работе в выходные / вне графика</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Положение о дежурстве на дому</t>
+          <t>Положение / распорядительный документ о дежурстве на дому</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Положение о дежурстве на дому</t>
+          <t>Положение / распорядительный документ о дежурстве на дому</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Наряд (вызов) на работу (смену, поездку)</t>
+          <t>Наряд / вызов / сообщение о явке на работу</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Локальные акты о документах первичного учета и поездной документации</t>
+          <t>ЛНА о документах первичного учета / поездной документации</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об исследовании на состояние опьянения</t>
+          <t>ЛНА об исследовании на состояние опьянения</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об исследовании на состояние опьянения</t>
+          <t>ЛНА об исследовании на состояние опьянения</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о предельно допустимом времени нахождения на работе с момента явки</t>
+          <t>ЛНА о междусменном отдыхе / предельном времени нахождения на работе</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о предельно допустимом времени нахождения на работе с момента явки</t>
+          <t>ЛНА о междусменном отдыхе / предельном времени нахождения на работе</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Порядок установления продолжительности непрерывной работы локомотивных бригад</t>
+          <t>Порядок / ЛНА о продолжительности непрерывной работы</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Порядок установления продолжительности непрерывной работы локомотивных бригад</t>
+          <t>Порядок / ЛНА о продолжительности непрерывной работы</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на увеличение продолжительности непрерывной работы</t>
+          <t>Письменное согласие на увеличение продолжительности работы / поездки / полетного времени</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Графики дежурств</t>
+          <t>Графики дежурств / несения дежурства</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Графики дежурств</t>
+          <t>Графики дежурств / несения дежурства</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности поездки и порядке ее увеличения</t>
+          <t>ЛНА о продолжительности поездки</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о продолжительности поездки и порядке ее увеличения</t>
+          <t>ЛНА о продолжительности поездки</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на увеличение продолжительности поездки / направление на специальные поезда</t>
+          <t>Письменное согласие на увеличение продолжительности работы / поездки / полетного времени</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о режиме рабочего времени при ликвидации последствий аварии или стихийного бедствия</t>
+          <t>ЛНА об особом режиме времени отдыха / при ликвидации аварии</t>
         </is>
       </c>
       <c r="E264" s="4" t="inlineStr">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о режиме рабочего времени при ликвидации последствий аварии или стихийного бедствия</t>
+          <t>ЛНА об особом режиме времени отдыха / при ликвидации аварии</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
@@ -17005,7 +17005,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на предоставление еженедельных дней отдыха в суммированном виде</t>
+          <t>Письменное согласие на предоставление / перенос суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о междусменном отдыхе локомотивных бригад</t>
+          <t>ЛНА о междусменном отдыхе / предельном времени нахождения на работе</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о междусменном отдыхе локомотивных бригад</t>
+          <t>ЛНА о междусменном отдыхе / предельном времени нахождения на работе</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о междусменном отдыхе проводников пассажирских вагонов</t>
+          <t>ЛНА о междусменном отдыхе / предельном времени нахождения на работе</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -17253,7 +17253,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о междусменном отдыхе проводников пассажирских вагонов</t>
+          <t>ЛНА о междусменном отдыхе / предельном времени нахождения на работе</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об особом режиме времени отдыха в период массовых пассажирских перевозок</t>
+          <t>ЛНА об особом режиме времени отдыха / при ликвидации аварии</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об особом режиме времени отдыха в период массовых пассажирских перевозок</t>
+          <t>ЛНА об особом режиме времени отдыха / при ликвидации аварии</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на сокращение междусменного отдыха</t>
+          <t>Письменное согласие / согласование на сокращение междусменного отдыха</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Решение об уменьшении междусменного отдыха</t>
+          <t>Решение о предоставлении перерыва для сна / уменьшении междусменного отдыха</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Решение об уменьшении междусменного отдыха</t>
+          <t>Решение о предоставлении перерыва для сна / уменьшении междусменного отдыха</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на сокращение междусменного отдыха</t>
+          <t>Письменное согласие / согласование на сокращение междусменного отдыха</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>График несения дежурства</t>
+          <t>Графики дежурств / несения дежурства</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Измененный график несения дежурства</t>
+          <t>Измененный график несения дежурства / службы</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с измененным графиком несения дежурства</t>
+          <t>Лист ознакомления с измененным графиком несения дежурства / службы</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Расписание занятий</t>
+          <t>Расписание занятий / выполнения работ / движения ВС</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Табель учета рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Распорядительный документ о дежурстве на дому в режиме ожидания</t>
+          <t>Положение / распорядительный документ о дежурстве на дому</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>График несения службы и специальной подготовки</t>
+          <t>График несения службы / специальной подготовки</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Измененный график несения службы и специальной подготовки</t>
+          <t>Измененный график несения дежурства / службы</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Табель учета рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -18493,7 +18493,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении нормативного времени прибытия при дежурстве на дому</t>
+          <t>ЛНА о нормативном времени прибытия / учете времени следования при дежурстве на дому</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Заявление о предоставлении места размещения в комнате отдыха при дежурстве на дому</t>
+          <t>Заявление о предоставлении места размещения при дежурстве на дому</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Решение об изменении режима труда и отдыха при аварийно-спасательных работах</t>
+          <t>Решение об изменении режима труда и отдыха при АСР</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
@@ -18803,7 +18803,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>График вахт (работ)</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>График вахт (работ)</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E302" s="4" t="inlineStr">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>Порядок предоставления выходных, праздничных и суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>Порядок предоставления выходных, праздничных и суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E304" s="4" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>Журнал учета служебного времени и предоставления дополнительных суток отдыха</t>
+          <t>Документы / журнал учета времени дежурства на дому</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
@@ -19485,7 +19485,7 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на выполнение работ, не входящих в круг должностных обязанностей</t>
+          <t>Письменное согласие на работы вне должностных обязанностей / саморемонт</t>
         </is>
       </c>
       <c r="E306" s="4" t="inlineStr">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>Перечень авральных работ</t>
+          <t>Перечень / ЛНА об авральных работах</t>
         </is>
       </c>
       <c r="E308" s="4" t="inlineStr">
@@ -19671,7 +19671,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение о производстве аварийных и авральных работ</t>
+          <t>Распоряжение о производстве аварийных / авральных работ</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E312" s="4" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками работы и (или) сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E314" s="4" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики работы и (или) сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики работы и (или) сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E316" s="4" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении рабочего дня с удлиненными перерывами</t>
+          <t>ЛНА об установлении рабочего дня с удлиненными перерывами</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт об установлении рабочего дня с удлиненными перерывами</t>
+          <t>ЛНА об установлении рабочего дня с удлиненными перерывами</t>
         </is>
       </c>
       <c r="E318" s="4" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>Табель учета рабочего времени</t>
+          <t>Табель / учетные записи / документы учета рабочего (служебного) времени</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -20353,7 +20353,7 @@
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>Приказ о привлечении к сверхурочным работам</t>
+          <t>Приказ / распоряжение о привлечении к сверхурочной работе / работе в выходные</t>
         </is>
       </c>
       <c r="E320" s="4" t="inlineStr">
@@ -20415,7 +20415,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>Приказ о привлечении к сверхурочным работам</t>
+          <t>Приказ / распоряжение о привлечении к сверхурочной работе / работе в выходные</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к сверхурочной работе</t>
+          <t>Письменное согласие на привлечение к сверхурочной работе / работе в выходные / вне графика</t>
         </is>
       </c>
       <c r="E322" s="4" t="inlineStr">
@@ -20725,7 +20725,7 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>Соглашение о разделении ежегодного оплачиваемого отпуска на части</t>
+          <t>Соглашение о разделении отпуска на части</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>Заявление о замене части отпуска денежной компенсацией</t>
+          <t>Заявление о предоставлении / замене дней отдыха</t>
         </is>
       </c>
       <c r="E328" s="4" t="inlineStr">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о введении режима гибкого рабочего времени</t>
+          <t>ЛНА о введении режима гибкого рабочего времени</t>
         </is>
       </c>
       <c r="E330" s="4" t="inlineStr">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E332" s="4" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>Лист ознакомления с графиками сменности</t>
+          <t>Лист ознакомления с графиками работы / сменности</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>Графики сменности</t>
+          <t>Графики работы / сменности</t>
         </is>
       </c>
       <c r="E334" s="4" t="inlineStr">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>Измененные графики сменности</t>
+          <t>Измененные графики работы / сменности</t>
         </is>
       </c>
       <c r="E336" s="4" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>Приказ о привлечении к сверхурочным работам</t>
+          <t>Приказ / распоряжение о привлечении к сверхурочной работе / работе в выходные</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>Приказ о привлечении к сверхурочным работам</t>
+          <t>Приказ / распоряжение о привлечении к сверхурочной работе / работе в выходные</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к сверхурочной работе</t>
+          <t>Письменное согласие на привлечение к сверхурочной работе / работе в выходные / вне графика</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>Письменное распоряжение (приказ) о привлечении к работе в выходные и нерабочие праздничные дни</t>
+          <t>Приказ / распоряжение о привлечении к сверхурочной работе / работе в выходные</t>
         </is>
       </c>
       <c r="E340" s="4" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>Письменное распоряжение (приказ) о привлечении к работе в выходные и нерабочие праздничные дни</t>
+          <t>Приказ / распоряжение о привлечении к сверхурочной работе / работе в выходные</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr">
@@ -21717,7 +21717,7 @@
       </c>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к работе вне графика / в выходные и нерабочие праздничные дни</t>
+          <t>Письменное согласие на привлечение к сверхурочной работе / работе в выходные / вне графика</t>
         </is>
       </c>
       <c r="E342" s="4" t="inlineStr">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>Приказ (ЛНА) / порядок о введении суммированного учета рабочего / служебного времени</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr">
@@ -21841,7 +21841,7 @@
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>Графики и расписания работы (вахт)</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E344" s="4" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение (приказ) об установлении суточного дежурства</t>
+          <t>Распоряжение (приказ) об установлении суточного / круглосуточного дежурства</t>
         </is>
       </c>
       <c r="E346" s="4" t="inlineStr">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на привлечение к работам по саморемонту судов</t>
+          <t>Письменное согласие на работы вне должностных обязанностей / саморемонт</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>Заявление о предоставлении дней отдыха во время нахождения судна в море</t>
+          <t>Заявление о предоставлении / замене дней отдыха</t>
         </is>
       </c>
       <c r="E348" s="4" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение о производстве аварийных и авральных работ</t>
+          <t>Распоряжение о производстве аварийных / авральных работ</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr">
@@ -22337,7 +22337,7 @@
       </c>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>График вахт (работ)</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E352" s="4" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>График вахт (работ)</t>
+          <t>Графики / расписания вахт (работ)</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="D354" s="10" t="inlineStr">
         <is>
-          <t>Распоряжение (приказ) об установлении суточного дежурства</t>
+          <t>Распоряжение (приказ) об установлении суточного / круглосуточного дежурства</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на выполнение работ, не входящих в круг должностных обязанностей</t>
+          <t>Письменное согласие на работы вне должностных обязанностей / саморемонт</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>Расценки оплаты работ, не входящих в круг должностных обязанностей</t>
+          <t>Расценки оплаты работ вне должностных обязанностей</t>
         </is>
       </c>
       <c r="E356" s="4" t="inlineStr">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>Расценки оплаты работ, не входящих в круг должностных обязанностей</t>
+          <t>Расценки оплаты работ вне должностных обязанностей</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>Порядок предоставления выходных, праздничных и суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E358" s="4" t="inlineStr">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>Порядок предоставления выходных, праздничных и суммированных дней отдыха</t>
+          <t>График / порядок предоставления суммированных дней отдыха</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>Письменное согласие на оплату работы в выходные и праздничные дни вместо дней отдыха</t>
+          <t>Письменное согласие на оплату вместо дней отдыха / переработки</t>
         </is>
       </c>
       <c r="E360" s="4" t="inlineStr">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>Перечень авральных работ</t>
+          <t>Перечень / ЛНА об авральных работах</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>Распоряжение о производстве аварийных и авральных работ</t>
+          <t>Распоряжение о производстве аварийных / авральных работ</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr">
